--- a/rebuttal_auc_original/AUC_rebuttal_results.xlsx
+++ b/rebuttal_auc_original/AUC_rebuttal_results.xlsx
@@ -879,42 +879,18 @@
           <t>ZOFOGDA-M=floor(sqrt(d))</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0.8746726524504302</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0.0001489168051914861</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0.7750488623372792</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>2.882236726234723e-05</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.7074107142857143</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>2.029837285679557e-05</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0.97309194914278</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>6.856960597446964e-06</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.8999581251176598</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>6.421515303778343e-07</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0.8839943190457583</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>7.078081468791267e-06</v>
-      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1738,36 +1714,12 @@
           <t>ZOFOGDA-M=floor(sqrt(d))</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>0.8747 ± 0.0122</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.7750 ± 0.0054</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>0.7074 ± 0.0045</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>0.9731 ± 0.0026</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>0.9000 ± 0.0008</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>0.8840 ± 0.0027</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -3567,7 +3519,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>floor(sqrt(20))=4</t>
+          <t>floor(sqrt(20))=53</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -3575,30 +3527,18 @@
           <t>AUC最大化</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>0.8747 ± 0.0122</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>0.8792 ± 0.0106</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>1944000</v>
-      </c>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>本次干净复跑</t>
+          <t>等待运行</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4355,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>floor(sqrt(24))=4</t>
+          <t>floor(sqrt(24))=57</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -4423,30 +4363,18 @@
           <t>AUC最大化</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>0.7750 ± 0.0054</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>0.7819 ± 0.0113</t>
-        </is>
-      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>3600000</v>
-      </c>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>本次干净复跑</t>
+          <t>等待运行</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5191,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>floor(sqrt(4))=2</t>
+          <t>floor(sqrt(4))=27</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -5271,30 +5199,18 @@
           <t>AUC最大化</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>0.7074 ± 0.0045</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>0.7211 ± 0.0218</t>
-        </is>
-      </c>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>7722500</v>
-      </c>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="6" t="inlineStr"/>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>本次干净复跑</t>
+          <t>等待运行</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6027,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>floor(sqrt(57))=7</t>
+          <t>floor(sqrt(57))=86</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -6119,30 +6035,18 @@
           <t>AUC最大化</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>0.9731 ± 0.0026</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>0.9735 ± 0.0025</t>
-        </is>
-      </c>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>27600000</v>
-      </c>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>本次干净复跑</t>
+          <t>等待运行</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6863,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>floor(sqrt(123))=11</t>
+          <t>floor(sqrt(123))=126</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -6967,30 +6871,18 @@
           <t>AUC最大化</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>0.9000 ± 0.0008</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>0.9000 ± 0.0007</t>
-        </is>
-      </c>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="I70" s="6" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="J70" s="6" t="n">
-        <v>374451500</v>
-      </c>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr"/>
+      <c r="J70" s="6" t="inlineStr"/>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>本次干净复跑</t>
+          <t>等待运行</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7699,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>floor(sqrt(22))=4</t>
+          <t>floor(sqrt(22))=55</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -7815,30 +7707,18 @@
           <t>AUC最大化</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>0.8840 ± 0.0027</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>0.8844 ± 0.0029</t>
-        </is>
-      </c>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="I86" s="6" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="J86" s="6" t="n">
-        <v>224955000</v>
-      </c>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="6" t="inlineStr"/>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>本次干净复跑</t>
+          <t>等待运行</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8470,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -8684,7 +8564,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -8778,7 +8658,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -8872,7 +8752,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -8966,7 +8846,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -9060,7 +8940,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -9154,7 +9034,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -9248,7 +9128,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -9342,7 +9222,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -9436,7 +9316,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -9530,7 +9410,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -9718,7 +9598,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -9812,7 +9692,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -9906,7 +9786,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -10000,7 +9880,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -10282,7 +10162,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -10470,7 +10350,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -10564,7 +10444,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -10658,7 +10538,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -10752,7 +10632,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -10846,7 +10726,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -10940,7 +10820,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -11034,7 +10914,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -11124,11 +11004,11 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_climate_M_4_s14_164cdf6</t>
+          <t>auc_zofosgda_climate_M_53_s14_4d43319</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -11147,82 +11027,44 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>0.8821548821548821</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>0.8877665544332211</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>328</v>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>22.518</v>
-      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="S29" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T29" s="6" t="n">
-        <v>1944000</v>
-      </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s14_164cdf6/zofoGDA_auc_climate_epochs500_seed14_batch128_gamma0.01_lam0.01_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s14_164cdf6/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W29" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s14_164cdf6/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X29" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_climate_M_4_s14_164cdf6.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr"/>
+      <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_climate_M_4_s42_78e7da8</t>
+          <t>auc_zofosgda_climate_M_53_s42_490e401</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -11241,82 +11083,44 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>0.8843995510662177</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0.8855218855218855</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>385</v>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>22.617</v>
-      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="S30" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T30" s="6" t="n">
-        <v>1944000</v>
-      </c>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s42_78e7da8/zofoGDA_auc_climate_epochs500_seed42_batch128_gamma0.01_lam0.01_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V30" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s42_78e7da8/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W30" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s42_78e7da8/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X30" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_climate_M_4_s42_78e7da8.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="6" t="inlineStr"/>
+      <c r="R30" s="6" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
+      <c r="U30" s="6" t="inlineStr"/>
+      <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_climate_M_4_s81_0ba1901</t>
+          <t>auc_zofosgda_climate_M_53_s81_a3a5b47</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -11335,73 +11139,35 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>0.8574635241301908</v>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v>0.8641975308641975</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>213</v>
-      </c>
-      <c r="O31" s="6" t="n">
-        <v>20.837</v>
-      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr"/>
       <c r="P31" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="S31" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T31" s="6" t="n">
-        <v>1944000</v>
-      </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s81_0ba1901/zofoGDA_auc_climate_epochs500_seed81_batch128_gamma0.01_lam0.01_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s81_0ba1901/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_climate_M_4_s81_0ba1901/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X31" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_climate_M_4_s81_0ba1901.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr"/>
+      <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -11410,7 +11176,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -11504,7 +11270,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -11598,7 +11364,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -11692,7 +11458,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -11786,7 +11552,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -11880,7 +11646,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -11974,7 +11740,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -12068,7 +11834,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -12162,7 +11928,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -12256,7 +12022,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -12350,7 +12116,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -12444,7 +12210,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -12538,7 +12304,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -12632,7 +12398,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -12726,7 +12492,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -12820,7 +12586,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -12914,7 +12680,7 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -13008,7 +12774,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -13102,7 +12868,7 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -13196,7 +12962,7 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -13290,7 +13056,7 @@
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -13384,7 +13150,7 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -13478,7 +13244,7 @@
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -13572,7 +13338,7 @@
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
@@ -13666,7 +13432,7 @@
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
@@ -13760,7 +13526,7 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
@@ -13854,7 +13620,7 @@
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
@@ -14136,7 +13902,7 @@
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
@@ -14230,7 +13996,7 @@
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
@@ -14324,7 +14090,7 @@
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
@@ -14418,7 +14184,7 @@
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
@@ -14512,7 +14278,7 @@
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
@@ -14700,7 +14466,7 @@
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
@@ -14888,7 +14654,7 @@
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
@@ -14982,7 +14748,7 @@
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
@@ -15076,7 +14842,7 @@
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
@@ -15170,7 +14936,7 @@
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
@@ -15264,7 +15030,7 @@
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
@@ -15358,7 +15124,7 @@
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
@@ -15452,7 +15218,7 @@
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
@@ -15546,7 +15312,7 @@
         </is>
       </c>
       <c r="B76" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
@@ -15640,7 +15406,7 @@
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
@@ -15734,7 +15500,7 @@
         </is>
       </c>
       <c r="B78" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
@@ -15828,7 +15594,7 @@
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
@@ -16110,7 +15876,7 @@
         </is>
       </c>
       <c r="B82" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
@@ -16204,7 +15970,7 @@
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
@@ -16298,7 +16064,7 @@
         </is>
       </c>
       <c r="B84" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
@@ -16392,7 +16158,7 @@
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
@@ -16486,7 +16252,7 @@
         </is>
       </c>
       <c r="B86" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
@@ -16580,7 +16346,7 @@
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
@@ -16674,7 +16440,7 @@
         </is>
       </c>
       <c r="B88" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
@@ -16768,7 +16534,7 @@
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
@@ -16862,7 +16628,7 @@
         </is>
       </c>
       <c r="B90" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
@@ -16956,7 +16722,7 @@
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
@@ -17046,11 +16812,11 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_german_M_4_s14_204e4c9</t>
+          <t>auc_zofosgda_german_M_57_s14_0575028</t>
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
@@ -17069,78 +16835,40 @@
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I92" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="6" t="n">
-        <v>0.7826086956521739</v>
-      </c>
-      <c r="M92" s="6" t="n">
-        <v>0.7977652395176458</v>
-      </c>
-      <c r="N92" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="O92" s="6" t="n">
-        <v>33.835</v>
-      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr"/>
+      <c r="J92" s="6" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr"/>
+      <c r="L92" s="6" t="inlineStr"/>
+      <c r="M92" s="6" t="inlineStr"/>
+      <c r="N92" s="6" t="inlineStr"/>
+      <c r="O92" s="6" t="inlineStr"/>
       <c r="P92" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q92" s="6" t="n">
-        <v>3500</v>
-      </c>
-      <c r="R92" s="6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="S92" s="6" t="n">
-        <v>3500</v>
-      </c>
-      <c r="T92" s="6" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="U92" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s14_204e4c9/zofoGDA_auc_german_epochs500_seed14_batch128_gamma0.005_lam0.005_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V92" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s14_204e4c9/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W92" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s14_204e4c9/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X92" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_german_M_4_s14_204e4c9.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q92" s="6" t="inlineStr"/>
+      <c r="R92" s="6" t="inlineStr"/>
+      <c r="S92" s="6" t="inlineStr"/>
+      <c r="T92" s="6" t="inlineStr"/>
+      <c r="U92" s="6" t="inlineStr"/>
+      <c r="V92" s="6" t="inlineStr"/>
+      <c r="W92" s="6" t="inlineStr"/>
+      <c r="X92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_german_M_4_s42_956b49e</t>
+          <t>auc_zofosgda_german_M_57_s42_39cf2cc</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
@@ -17163,82 +16891,44 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G93" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I93" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J93" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K93" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="6" t="n">
-        <v>0.7718774200685916</v>
-      </c>
-      <c r="M93" s="6" t="n">
-        <v>0.7730943688461113</v>
-      </c>
-      <c r="N93" s="6" t="n">
-        <v>202</v>
-      </c>
-      <c r="O93" s="6" t="n">
-        <v>33.604</v>
-      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr"/>
+      <c r="J93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr"/>
+      <c r="M93" s="6" t="inlineStr"/>
+      <c r="N93" s="6" t="inlineStr"/>
+      <c r="O93" s="6" t="inlineStr"/>
       <c r="P93" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q93" s="6" t="n">
-        <v>3500</v>
-      </c>
-      <c r="R93" s="6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="S93" s="6" t="n">
-        <v>3500</v>
-      </c>
-      <c r="T93" s="6" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="U93" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s42_956b49e/zofoGDA_auc_german_epochs500_seed42_batch128_gamma0.005_lam0.005_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V93" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s42_956b49e/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W93" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s42_956b49e/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X93" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_german_M_4_s42_956b49e.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q93" s="6" t="inlineStr"/>
+      <c r="R93" s="6" t="inlineStr"/>
+      <c r="S93" s="6" t="inlineStr"/>
+      <c r="T93" s="6" t="inlineStr"/>
+      <c r="U93" s="6" t="inlineStr"/>
+      <c r="V93" s="6" t="inlineStr"/>
+      <c r="W93" s="6" t="inlineStr"/>
+      <c r="X93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_german_M_4_s81_4d55b88</t>
+          <t>auc_zofosgda_german_M_57_s81_c2f7944</t>
         </is>
       </c>
       <c r="B94" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
@@ -17257,73 +16947,35 @@
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G94" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="6" t="n">
-        <v>0.7706604712910721</v>
-      </c>
-      <c r="M94" s="6" t="n">
-        <v>0.7747538444518199</v>
-      </c>
-      <c r="N94" s="6" t="n">
-        <v>447</v>
-      </c>
-      <c r="O94" s="6" t="n">
-        <v>34.12</v>
-      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr"/>
+      <c r="J94" s="6" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr"/>
+      <c r="L94" s="6" t="inlineStr"/>
+      <c r="M94" s="6" t="inlineStr"/>
+      <c r="N94" s="6" t="inlineStr"/>
+      <c r="O94" s="6" t="inlineStr"/>
       <c r="P94" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q94" s="6" t="n">
-        <v>3500</v>
-      </c>
-      <c r="R94" s="6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="S94" s="6" t="n">
-        <v>3500</v>
-      </c>
-      <c r="T94" s="6" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="U94" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s81_4d55b88/zofoGDA_auc_german_epochs500_seed81_batch128_gamma0.005_lam0.005_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V94" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s81_4d55b88/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W94" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_german_M_4_s81_4d55b88/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X94" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_german_M_4_s81_4d55b88.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q94" s="6" t="inlineStr"/>
+      <c r="R94" s="6" t="inlineStr"/>
+      <c r="S94" s="6" t="inlineStr"/>
+      <c r="T94" s="6" t="inlineStr"/>
+      <c r="U94" s="6" t="inlineStr"/>
+      <c r="V94" s="6" t="inlineStr"/>
+      <c r="W94" s="6" t="inlineStr"/>
+      <c r="X94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -17332,7 +16984,7 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
@@ -17426,7 +17078,7 @@
         </is>
       </c>
       <c r="B96" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
@@ -17520,7 +17172,7 @@
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
@@ -17614,7 +17266,7 @@
         </is>
       </c>
       <c r="B98" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
@@ -17708,7 +17360,7 @@
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
@@ -17802,7 +17454,7 @@
         </is>
       </c>
       <c r="B100" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
@@ -17896,7 +17548,7 @@
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
@@ -17990,7 +17642,7 @@
         </is>
       </c>
       <c r="B102" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
@@ -18084,7 +17736,7 @@
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
@@ -18178,7 +17830,7 @@
         </is>
       </c>
       <c r="B104" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
@@ -18272,7 +17924,7 @@
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
@@ -18366,7 +18018,7 @@
         </is>
       </c>
       <c r="B106" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
@@ -18460,7 +18112,7 @@
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
@@ -18648,7 +18300,7 @@
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
@@ -18742,7 +18394,7 @@
         </is>
       </c>
       <c r="B110" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
@@ -18836,7 +18488,7 @@
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
@@ -18930,7 +18582,7 @@
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
@@ -19024,7 +18676,7 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
@@ -19118,7 +18770,7 @@
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
@@ -19212,7 +18864,7 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
@@ -19306,7 +18958,7 @@
         </is>
       </c>
       <c r="B116" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
@@ -19400,7 +19052,7 @@
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
@@ -19588,7 +19240,7 @@
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
@@ -19682,7 +19334,7 @@
         </is>
       </c>
       <c r="B120" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
@@ -19776,7 +19428,7 @@
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
@@ -19870,7 +19522,7 @@
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
@@ -20058,7 +19710,7 @@
         </is>
       </c>
       <c r="B124" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
@@ -20152,7 +19804,7 @@
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
@@ -20246,7 +19898,7 @@
         </is>
       </c>
       <c r="B126" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
@@ -20340,7 +19992,7 @@
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
@@ -20434,7 +20086,7 @@
         </is>
       </c>
       <c r="B128" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
@@ -20622,7 +20274,7 @@
         </is>
       </c>
       <c r="B130" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
@@ -20810,7 +20462,7 @@
         </is>
       </c>
       <c r="B132" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
@@ -20904,7 +20556,7 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
@@ -20998,7 +20650,7 @@
         </is>
       </c>
       <c r="B134" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
@@ -21186,7 +20838,7 @@
         </is>
       </c>
       <c r="B136" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
@@ -21280,7 +20932,7 @@
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
@@ -21374,7 +21026,7 @@
         </is>
       </c>
       <c r="B138" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
@@ -21468,7 +21120,7 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
@@ -21562,7 +21214,7 @@
         </is>
       </c>
       <c r="B140" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
@@ -21656,7 +21308,7 @@
         </is>
       </c>
       <c r="B141" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
@@ -21750,7 +21402,7 @@
         </is>
       </c>
       <c r="B142" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
@@ -21844,7 +21496,7 @@
         </is>
       </c>
       <c r="B143" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
@@ -21938,7 +21590,7 @@
         </is>
       </c>
       <c r="B144" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
@@ -22032,7 +21684,7 @@
         </is>
       </c>
       <c r="B145" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
@@ -22126,7 +21778,7 @@
         </is>
       </c>
       <c r="B146" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
@@ -22220,7 +21872,7 @@
         </is>
       </c>
       <c r="B147" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
@@ -22314,7 +21966,7 @@
         </is>
       </c>
       <c r="B148" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
@@ -22408,7 +22060,7 @@
         </is>
       </c>
       <c r="B149" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
@@ -22502,7 +22154,7 @@
         </is>
       </c>
       <c r="B150" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
@@ -22784,7 +22436,7 @@
         </is>
       </c>
       <c r="B153" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
@@ -22878,7 +22530,7 @@
         </is>
       </c>
       <c r="B154" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
@@ -22968,11 +22620,11 @@
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_svmguide1_M_2_s14_44ee4ba</t>
+          <t>auc_zofosgda_svmguide1_M_27_s14_217f669</t>
         </is>
       </c>
       <c r="B155" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
@@ -22991,82 +22643,44 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G155" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H155" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I155" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J155" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K155" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L155" s="6" t="n">
-        <v>0.7105357142857143</v>
-      </c>
-      <c r="M155" s="6" t="n">
-        <v>0.7105994897959184</v>
-      </c>
-      <c r="N155" s="6" t="n">
-        <v>496</v>
-      </c>
-      <c r="O155" s="6" t="n">
-        <v>108.76</v>
-      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr"/>
+      <c r="J155" s="6" t="inlineStr"/>
+      <c r="K155" s="6" t="inlineStr"/>
+      <c r="L155" s="6" t="inlineStr"/>
+      <c r="M155" s="6" t="inlineStr"/>
+      <c r="N155" s="6" t="inlineStr"/>
+      <c r="O155" s="6" t="inlineStr"/>
       <c r="P155" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q155" s="6" t="n">
-        <v>12500</v>
-      </c>
-      <c r="R155" s="6" t="n">
-        <v>62500</v>
-      </c>
-      <c r="S155" s="6" t="n">
-        <v>12500</v>
-      </c>
-      <c r="T155" s="6" t="n">
-        <v>7722500</v>
-      </c>
-      <c r="U155" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s14_44ee4ba/zofoGDA_auc_svmguide1_epochs500_seed14_batch128_gamma0.001_lam0.001_delta0.001q2_log.csv</t>
-        </is>
-      </c>
-      <c r="V155" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s14_44ee4ba/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W155" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s14_44ee4ba/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X155" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_svmguide1_M_2_s14_44ee4ba.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q155" s="6" t="inlineStr"/>
+      <c r="R155" s="6" t="inlineStr"/>
+      <c r="S155" s="6" t="inlineStr"/>
+      <c r="T155" s="6" t="inlineStr"/>
+      <c r="U155" s="6" t="inlineStr"/>
+      <c r="V155" s="6" t="inlineStr"/>
+      <c r="W155" s="6" t="inlineStr"/>
+      <c r="X155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_svmguide1_M_2_s42_855a14d</t>
+          <t>auc_zofosgda_svmguide1_M_27_s42_34e9b02</t>
         </is>
       </c>
       <c r="B156" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
@@ -23085,82 +22699,44 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G156" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H156" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I156" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J156" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K156" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L156" s="6" t="n">
-        <v>0.7010395408163266</v>
-      </c>
-      <c r="M156" s="6" t="n">
-        <v>0.7012755102040816</v>
-      </c>
-      <c r="N156" s="6" t="n">
-        <v>449</v>
-      </c>
-      <c r="O156" s="6" t="n">
-        <v>110.278</v>
-      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr"/>
+      <c r="J156" s="6" t="inlineStr"/>
+      <c r="K156" s="6" t="inlineStr"/>
+      <c r="L156" s="6" t="inlineStr"/>
+      <c r="M156" s="6" t="inlineStr"/>
+      <c r="N156" s="6" t="inlineStr"/>
+      <c r="O156" s="6" t="inlineStr"/>
       <c r="P156" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q156" s="6" t="n">
-        <v>12500</v>
-      </c>
-      <c r="R156" s="6" t="n">
-        <v>62500</v>
-      </c>
-      <c r="S156" s="6" t="n">
-        <v>12500</v>
-      </c>
-      <c r="T156" s="6" t="n">
-        <v>7722500</v>
-      </c>
-      <c r="U156" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s42_855a14d/zofoGDA_auc_svmguide1_epochs500_seed42_batch128_gamma0.001_lam0.001_delta0.001q2_log.csv</t>
-        </is>
-      </c>
-      <c r="V156" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s42_855a14d/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W156" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s42_855a14d/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X156" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_svmguide1_M_2_s42_855a14d.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q156" s="6" t="inlineStr"/>
+      <c r="R156" s="6" t="inlineStr"/>
+      <c r="S156" s="6" t="inlineStr"/>
+      <c r="T156" s="6" t="inlineStr"/>
+      <c r="U156" s="6" t="inlineStr"/>
+      <c r="V156" s="6" t="inlineStr"/>
+      <c r="W156" s="6" t="inlineStr"/>
+      <c r="X156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_svmguide1_M_2_s81_15f4762</t>
+          <t>auc_zofosgda_svmguide1_M_27_s81_0684bd7</t>
         </is>
       </c>
       <c r="B157" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
@@ -23179,73 +22755,35 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G157" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="H157" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I157" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J157" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K157" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" s="6" t="n">
-        <v>0.7106568877551021</v>
-      </c>
-      <c r="M157" s="6" t="n">
-        <v>0.7513775510204082</v>
-      </c>
-      <c r="N157" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O157" s="6" t="n">
-        <v>108.147</v>
-      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr"/>
+      <c r="J157" s="6" t="inlineStr"/>
+      <c r="K157" s="6" t="inlineStr"/>
+      <c r="L157" s="6" t="inlineStr"/>
+      <c r="M157" s="6" t="inlineStr"/>
+      <c r="N157" s="6" t="inlineStr"/>
+      <c r="O157" s="6" t="inlineStr"/>
       <c r="P157" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q157" s="6" t="n">
-        <v>12500</v>
-      </c>
-      <c r="R157" s="6" t="n">
-        <v>62500</v>
-      </c>
-      <c r="S157" s="6" t="n">
-        <v>12500</v>
-      </c>
-      <c r="T157" s="6" t="n">
-        <v>7722500</v>
-      </c>
-      <c r="U157" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s81_15f4762/zofoGDA_auc_svmguide1_epochs500_seed81_batch128_gamma0.001_lam0.001_delta0.001q2_log.csv</t>
-        </is>
-      </c>
-      <c r="V157" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s81_15f4762/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W157" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_svmguide1_M_2_s81_15f4762/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X157" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_svmguide1_M_2_s81_15f4762.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q157" s="6" t="inlineStr"/>
+      <c r="R157" s="6" t="inlineStr"/>
+      <c r="S157" s="6" t="inlineStr"/>
+      <c r="T157" s="6" t="inlineStr"/>
+      <c r="U157" s="6" t="inlineStr"/>
+      <c r="V157" s="6" t="inlineStr"/>
+      <c r="W157" s="6" t="inlineStr"/>
+      <c r="X157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -23348,7 +22886,7 @@
         </is>
       </c>
       <c r="B159" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
@@ -23442,7 +22980,7 @@
         </is>
       </c>
       <c r="B160" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
@@ -23630,7 +23168,7 @@
         </is>
       </c>
       <c r="B162" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
@@ -23818,7 +23356,7 @@
         </is>
       </c>
       <c r="B164" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
@@ -24006,7 +23544,7 @@
         </is>
       </c>
       <c r="B166" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
@@ -24100,7 +23638,7 @@
         </is>
       </c>
       <c r="B167" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
@@ -24194,7 +23732,7 @@
         </is>
       </c>
       <c r="B168" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
@@ -24382,7 +23920,7 @@
         </is>
       </c>
       <c r="B170" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
@@ -24476,7 +24014,7 @@
         </is>
       </c>
       <c r="B171" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
@@ -24570,7 +24108,7 @@
         </is>
       </c>
       <c r="B172" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
@@ -24758,7 +24296,7 @@
         </is>
       </c>
       <c r="B174" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
@@ -24852,7 +24390,7 @@
         </is>
       </c>
       <c r="B175" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
@@ -24946,7 +24484,7 @@
         </is>
       </c>
       <c r="B176" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
@@ -25040,7 +24578,7 @@
         </is>
       </c>
       <c r="B177" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
@@ -25134,7 +24672,7 @@
         </is>
       </c>
       <c r="B178" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
@@ -25228,7 +24766,7 @@
         </is>
       </c>
       <c r="B179" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
@@ -25322,7 +24860,7 @@
         </is>
       </c>
       <c r="B180" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
@@ -25416,7 +24954,7 @@
         </is>
       </c>
       <c r="B181" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
@@ -25510,7 +25048,7 @@
         </is>
       </c>
       <c r="B182" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
@@ -25698,7 +25236,7 @@
         </is>
       </c>
       <c r="B184" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
@@ -25792,7 +25330,7 @@
         </is>
       </c>
       <c r="B185" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
@@ -25886,7 +25424,7 @@
         </is>
       </c>
       <c r="B186" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
@@ -25980,7 +25518,7 @@
         </is>
       </c>
       <c r="B187" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
@@ -26074,7 +25612,7 @@
         </is>
       </c>
       <c r="B188" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
@@ -26168,7 +25706,7 @@
         </is>
       </c>
       <c r="B189" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
@@ -26262,7 +25800,7 @@
         </is>
       </c>
       <c r="B190" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
@@ -26356,7 +25894,7 @@
         </is>
       </c>
       <c r="B191" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
@@ -26450,7 +25988,7 @@
         </is>
       </c>
       <c r="B192" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
@@ -26544,7 +26082,7 @@
         </is>
       </c>
       <c r="B193" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
@@ -26732,7 +26270,7 @@
         </is>
       </c>
       <c r="B195" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
@@ -26826,7 +26364,7 @@
         </is>
       </c>
       <c r="B196" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
@@ -26920,7 +26458,7 @@
         </is>
       </c>
       <c r="B197" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
@@ -27014,7 +26552,7 @@
         </is>
       </c>
       <c r="B198" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
@@ -27108,7 +26646,7 @@
         </is>
       </c>
       <c r="B199" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
@@ -27296,7 +26834,7 @@
         </is>
       </c>
       <c r="B201" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
@@ -27390,7 +26928,7 @@
         </is>
       </c>
       <c r="B202" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
@@ -27484,7 +27022,7 @@
         </is>
       </c>
       <c r="B203" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
@@ -27578,7 +27116,7 @@
         </is>
       </c>
       <c r="B204" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
@@ -27766,7 +27304,7 @@
         </is>
       </c>
       <c r="B206" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27398,7 @@
         </is>
       </c>
       <c r="B207" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
@@ -27954,7 +27492,7 @@
         </is>
       </c>
       <c r="B208" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
@@ -28048,7 +27586,7 @@
         </is>
       </c>
       <c r="B209" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
@@ -28142,7 +27680,7 @@
         </is>
       </c>
       <c r="B210" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
@@ -28330,7 +27868,7 @@
         </is>
       </c>
       <c r="B212" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
@@ -28424,7 +27962,7 @@
         </is>
       </c>
       <c r="B213" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
@@ -28518,7 +28056,7 @@
         </is>
       </c>
       <c r="B214" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
@@ -28612,7 +28150,7 @@
         </is>
       </c>
       <c r="B215" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
@@ -28706,7 +28244,7 @@
         </is>
       </c>
       <c r="B216" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
@@ -28800,7 +28338,7 @@
         </is>
       </c>
       <c r="B217" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
@@ -28890,11 +28428,11 @@
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_spambase_M_7_s14_e8e8fe2</t>
+          <t>auc_zofosgda_spambase_M_86_s14_691154d</t>
         </is>
       </c>
       <c r="B218" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
@@ -28913,78 +28451,40 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G218" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H218" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I218" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J218" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K218" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L218" s="6" t="n">
-        <v>0.9721555733285938</v>
-      </c>
-      <c r="M218" s="6" t="n">
-        <v>0.9724912862742775</v>
-      </c>
-      <c r="N218" s="6" t="n">
-        <v>428</v>
-      </c>
-      <c r="O218" s="6" t="n">
-        <v>179.848</v>
-      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="inlineStr"/>
+      <c r="J218" s="6" t="inlineStr"/>
+      <c r="K218" s="6" t="inlineStr"/>
+      <c r="L218" s="6" t="inlineStr"/>
+      <c r="M218" s="6" t="inlineStr"/>
+      <c r="N218" s="6" t="inlineStr"/>
+      <c r="O218" s="6" t="inlineStr"/>
       <c r="P218" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q218" s="6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="R218" s="6" t="n">
-        <v>217500</v>
-      </c>
-      <c r="S218" s="6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="T218" s="6" t="n">
-        <v>27600000</v>
-      </c>
-      <c r="U218" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s14_e8e8fe2/zofoGDA_auc_spambase_epochs500_seed14_batch128_gamma0.04_lam0.04_delta0.001q7_log.csv</t>
-        </is>
-      </c>
-      <c r="V218" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s14_e8e8fe2/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W218" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s14_e8e8fe2/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X218" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_spambase_M_7_s14_e8e8fe2.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q218" s="6" t="inlineStr"/>
+      <c r="R218" s="6" t="inlineStr"/>
+      <c r="S218" s="6" t="inlineStr"/>
+      <c r="T218" s="6" t="inlineStr"/>
+      <c r="U218" s="6" t="inlineStr"/>
+      <c r="V218" s="6" t="inlineStr"/>
+      <c r="W218" s="6" t="inlineStr"/>
+      <c r="X218" s="6" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_spambase_M_7_s42_03edb97</t>
+          <t>auc_zofosgda_spambase_M_86_s42_77e4e79</t>
         </is>
       </c>
       <c r="B219" s="6" t="n">
@@ -29007,78 +28507,40 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G219" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H219" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I219" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J219" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K219" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L219" s="6" t="n">
-        <v>0.9704572607798414</v>
-      </c>
-      <c r="M219" s="6" t="n">
-        <v>0.9710398214797041</v>
-      </c>
-      <c r="N219" s="6" t="n">
-        <v>469</v>
-      </c>
-      <c r="O219" s="6" t="n">
-        <v>180.743</v>
-      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="inlineStr"/>
+      <c r="J219" s="6" t="inlineStr"/>
+      <c r="K219" s="6" t="inlineStr"/>
+      <c r="L219" s="6" t="inlineStr"/>
+      <c r="M219" s="6" t="inlineStr"/>
+      <c r="N219" s="6" t="inlineStr"/>
+      <c r="O219" s="6" t="inlineStr"/>
       <c r="P219" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q219" s="6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="R219" s="6" t="n">
-        <v>217500</v>
-      </c>
-      <c r="S219" s="6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="T219" s="6" t="n">
-        <v>27600000</v>
-      </c>
-      <c r="U219" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s42_03edb97/zofoGDA_auc_spambase_epochs500_seed42_batch128_gamma0.04_lam0.04_delta0.001q7_log.csv</t>
-        </is>
-      </c>
-      <c r="V219" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s42_03edb97/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W219" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s42_03edb97/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X219" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_spambase_M_7_s42_03edb97.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q219" s="6" t="inlineStr"/>
+      <c r="R219" s="6" t="inlineStr"/>
+      <c r="S219" s="6" t="inlineStr"/>
+      <c r="T219" s="6" t="inlineStr"/>
+      <c r="U219" s="6" t="inlineStr"/>
+      <c r="V219" s="6" t="inlineStr"/>
+      <c r="W219" s="6" t="inlineStr"/>
+      <c r="X219" s="6" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_spambase_M_7_s81_7a58784</t>
+          <t>auc_zofosgda_spambase_M_86_s81_e2ca869</t>
         </is>
       </c>
       <c r="B220" s="6" t="n">
@@ -29101,73 +28563,35 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G220" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="H220" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I220" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J220" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K220" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L220" s="6" t="n">
-        <v>0.9766630133199048</v>
-      </c>
-      <c r="M220" s="6" t="n">
-        <v>0.9768308697927466</v>
-      </c>
-      <c r="N220" s="6" t="n">
-        <v>494</v>
-      </c>
-      <c r="O220" s="6" t="n">
-        <v>181.541</v>
-      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr"/>
+      <c r="J220" s="6" t="inlineStr"/>
+      <c r="K220" s="6" t="inlineStr"/>
+      <c r="L220" s="6" t="inlineStr"/>
+      <c r="M220" s="6" t="inlineStr"/>
+      <c r="N220" s="6" t="inlineStr"/>
+      <c r="O220" s="6" t="inlineStr"/>
       <c r="P220" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q220" s="6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="R220" s="6" t="n">
-        <v>217500</v>
-      </c>
-      <c r="S220" s="6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="T220" s="6" t="n">
-        <v>27600000</v>
-      </c>
-      <c r="U220" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s81_7a58784/zofoGDA_auc_spambase_epochs500_seed81_batch128_gamma0.04_lam0.04_delta0.001q7_log.csv</t>
-        </is>
-      </c>
-      <c r="V220" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s81_7a58784/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W220" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_spambase_M_7_s81_7a58784/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X220" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_spambase_M_7_s81_7a58784.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q220" s="6" t="inlineStr"/>
+      <c r="R220" s="6" t="inlineStr"/>
+      <c r="S220" s="6" t="inlineStr"/>
+      <c r="T220" s="6" t="inlineStr"/>
+      <c r="U220" s="6" t="inlineStr"/>
+      <c r="V220" s="6" t="inlineStr"/>
+      <c r="W220" s="6" t="inlineStr"/>
+      <c r="X220" s="6" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -29270,7 +28694,7 @@
         </is>
       </c>
       <c r="B222" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
@@ -29364,7 +28788,7 @@
         </is>
       </c>
       <c r="B223" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
@@ -29458,7 +28882,7 @@
         </is>
       </c>
       <c r="B224" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
@@ -29552,7 +28976,7 @@
         </is>
       </c>
       <c r="B225" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
@@ -29646,7 +29070,7 @@
         </is>
       </c>
       <c r="B226" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
@@ -29740,7 +29164,7 @@
         </is>
       </c>
       <c r="B227" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
@@ -29834,7 +29258,7 @@
         </is>
       </c>
       <c r="B228" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
@@ -29928,7 +29352,7 @@
         </is>
       </c>
       <c r="B229" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
@@ -30022,7 +29446,7 @@
         </is>
       </c>
       <c r="B230" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
@@ -30116,7 +29540,7 @@
         </is>
       </c>
       <c r="B231" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
@@ -30210,7 +29634,7 @@
         </is>
       </c>
       <c r="B232" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
@@ -30304,7 +29728,7 @@
         </is>
       </c>
       <c r="B233" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
@@ -30398,7 +29822,7 @@
         </is>
       </c>
       <c r="B234" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
@@ -30492,7 +29916,7 @@
         </is>
       </c>
       <c r="B235" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
@@ -30586,7 +30010,7 @@
         </is>
       </c>
       <c r="B236" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
@@ -30774,7 +30198,7 @@
         </is>
       </c>
       <c r="B238" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
@@ -30868,7 +30292,7 @@
         </is>
       </c>
       <c r="B239" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
@@ -30962,7 +30386,7 @@
         </is>
       </c>
       <c r="B240" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
@@ -31056,7 +30480,7 @@
         </is>
       </c>
       <c r="B241" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
@@ -31244,7 +30668,7 @@
         </is>
       </c>
       <c r="B243" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
@@ -31432,7 +30856,7 @@
         </is>
       </c>
       <c r="B245" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
@@ -31526,7 +30950,7 @@
         </is>
       </c>
       <c r="B246" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
@@ -31620,7 +31044,7 @@
         </is>
       </c>
       <c r="B247" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
@@ -31714,7 +31138,7 @@
         </is>
       </c>
       <c r="B248" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C248" s="6" t="inlineStr">
         <is>
@@ -31808,7 +31232,7 @@
         </is>
       </c>
       <c r="B249" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
@@ -31902,7 +31326,7 @@
         </is>
       </c>
       <c r="B250" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C250" s="6" t="inlineStr">
         <is>
@@ -31996,7 +31420,7 @@
         </is>
       </c>
       <c r="B251" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
@@ -32090,7 +31514,7 @@
         </is>
       </c>
       <c r="B252" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
@@ -32184,7 +31608,7 @@
         </is>
       </c>
       <c r="B253" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
@@ -32372,7 +31796,7 @@
         </is>
       </c>
       <c r="B255" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
@@ -32466,7 +31890,7 @@
         </is>
       </c>
       <c r="B256" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C256" s="6" t="inlineStr">
         <is>
@@ -32560,7 +31984,7 @@
         </is>
       </c>
       <c r="B257" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
@@ -32654,7 +32078,7 @@
         </is>
       </c>
       <c r="B258" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C258" s="6" t="inlineStr">
         <is>
@@ -32748,7 +32172,7 @@
         </is>
       </c>
       <c r="B259" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
@@ -32842,7 +32266,7 @@
         </is>
       </c>
       <c r="B260" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C260" s="6" t="inlineStr">
         <is>
@@ -32936,7 +32360,7 @@
         </is>
       </c>
       <c r="B261" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
@@ -33030,7 +32454,7 @@
         </is>
       </c>
       <c r="B262" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C262" s="6" t="inlineStr">
         <is>
@@ -33124,7 +32548,7 @@
         </is>
       </c>
       <c r="B263" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
@@ -33218,7 +32642,7 @@
         </is>
       </c>
       <c r="B264" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C264" s="6" t="inlineStr">
         <is>
@@ -33312,7 +32736,7 @@
         </is>
       </c>
       <c r="B265" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
@@ -33406,7 +32830,7 @@
         </is>
       </c>
       <c r="B266" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C266" s="6" t="inlineStr">
         <is>
@@ -33500,7 +32924,7 @@
         </is>
       </c>
       <c r="B267" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
@@ -33594,7 +33018,7 @@
         </is>
       </c>
       <c r="B268" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C268" s="6" t="inlineStr">
         <is>
@@ -33782,7 +33206,7 @@
         </is>
       </c>
       <c r="B270" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C270" s="6" t="inlineStr">
         <is>
@@ -33876,7 +33300,7 @@
         </is>
       </c>
       <c r="B271" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
@@ -34064,7 +33488,7 @@
         </is>
       </c>
       <c r="B273" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
@@ -34252,7 +33676,7 @@
         </is>
       </c>
       <c r="B275" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
@@ -34530,7 +33954,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_a9a_M_11_s14_5c14307</t>
+          <t>auc_zofosgda_a9a_M_126_s14_25a1f6c</t>
         </is>
       </c>
       <c r="B278" s="6" t="n">
@@ -34553,78 +33977,40 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G278" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H278" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I278" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J278" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K278" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L278" s="6" t="n">
-        <v>0.9005507892209537</v>
-      </c>
-      <c r="M278" s="6" t="n">
-        <v>0.9005846836205575</v>
-      </c>
-      <c r="N278" s="6" t="n">
-        <v>496</v>
-      </c>
-      <c r="O278" s="6" t="n">
-        <v>2148.61</v>
-      </c>
+      <c r="H278" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I278" s="6" t="inlineStr"/>
+      <c r="J278" s="6" t="inlineStr"/>
+      <c r="K278" s="6" t="inlineStr"/>
+      <c r="L278" s="6" t="inlineStr"/>
+      <c r="M278" s="6" t="inlineStr"/>
+      <c r="N278" s="6" t="inlineStr"/>
+      <c r="O278" s="6" t="inlineStr"/>
       <c r="P278" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q278" s="6" t="n">
-        <v>127500</v>
-      </c>
-      <c r="R278" s="6" t="n">
-        <v>2932500</v>
-      </c>
-      <c r="S278" s="6" t="n">
-        <v>127500</v>
-      </c>
-      <c r="T278" s="6" t="n">
-        <v>374451500</v>
-      </c>
-      <c r="U278" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s14_5c14307/zofoGDA_auc_a9a_epochs500_seed14_batch128_gamma0.01_lam0.01_delta0.001q11_log.csv</t>
-        </is>
-      </c>
-      <c r="V278" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s14_5c14307/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W278" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s14_5c14307/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X278" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_a9a_M_11_s14_5c14307.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q278" s="6" t="inlineStr"/>
+      <c r="R278" s="6" t="inlineStr"/>
+      <c r="S278" s="6" t="inlineStr"/>
+      <c r="T278" s="6" t="inlineStr"/>
+      <c r="U278" s="6" t="inlineStr"/>
+      <c r="V278" s="6" t="inlineStr"/>
+      <c r="W278" s="6" t="inlineStr"/>
+      <c r="X278" s="6" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_a9a_M_11_s42_85f5f45</t>
+          <t>auc_zofosgda_a9a_M_126_s42_3c1630f</t>
         </is>
       </c>
       <c r="B279" s="6" t="n">
@@ -34647,78 +34033,40 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G279" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H279" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I279" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J279" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K279" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L279" s="6" t="n">
-        <v>0.9004983271305118</v>
-      </c>
-      <c r="M279" s="6" t="n">
-        <v>0.9005445477167699</v>
-      </c>
-      <c r="N279" s="6" t="n">
-        <v>492</v>
-      </c>
-      <c r="O279" s="6" t="n">
-        <v>2171.008</v>
-      </c>
+      <c r="H279" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I279" s="6" t="inlineStr"/>
+      <c r="J279" s="6" t="inlineStr"/>
+      <c r="K279" s="6" t="inlineStr"/>
+      <c r="L279" s="6" t="inlineStr"/>
+      <c r="M279" s="6" t="inlineStr"/>
+      <c r="N279" s="6" t="inlineStr"/>
+      <c r="O279" s="6" t="inlineStr"/>
       <c r="P279" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q279" s="6" t="n">
-        <v>127500</v>
-      </c>
-      <c r="R279" s="6" t="n">
-        <v>2932500</v>
-      </c>
-      <c r="S279" s="6" t="n">
-        <v>127500</v>
-      </c>
-      <c r="T279" s="6" t="n">
-        <v>374451500</v>
-      </c>
-      <c r="U279" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s42_85f5f45/zofoGDA_auc_a9a_epochs500_seed42_batch128_gamma0.01_lam0.01_delta0.001q11_log.csv</t>
-        </is>
-      </c>
-      <c r="V279" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s42_85f5f45/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W279" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s42_85f5f45/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X279" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_a9a_M_11_s42_85f5f45.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q279" s="6" t="inlineStr"/>
+      <c r="R279" s="6" t="inlineStr"/>
+      <c r="S279" s="6" t="inlineStr"/>
+      <c r="T279" s="6" t="inlineStr"/>
+      <c r="U279" s="6" t="inlineStr"/>
+      <c r="V279" s="6" t="inlineStr"/>
+      <c r="W279" s="6" t="inlineStr"/>
+      <c r="X279" s="6" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_a9a_M_11_s81_90b80c5</t>
+          <t>auc_zofosgda_a9a_M_126_s81_5b6f179</t>
         </is>
       </c>
       <c r="B280" s="6" t="n">
@@ -34741,73 +34089,35 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G280" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="H280" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I280" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L280" s="6" t="n">
-        <v>0.8988252590015141</v>
-      </c>
-      <c r="M280" s="6" t="n">
-        <v>0.8990016207001316</v>
-      </c>
-      <c r="N280" s="6" t="n">
-        <v>471</v>
-      </c>
-      <c r="O280" s="6" t="n">
-        <v>2215.444</v>
-      </c>
+      <c r="H280" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I280" s="6" t="inlineStr"/>
+      <c r="J280" s="6" t="inlineStr"/>
+      <c r="K280" s="6" t="inlineStr"/>
+      <c r="L280" s="6" t="inlineStr"/>
+      <c r="M280" s="6" t="inlineStr"/>
+      <c r="N280" s="6" t="inlineStr"/>
+      <c r="O280" s="6" t="inlineStr"/>
       <c r="P280" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q280" s="6" t="n">
-        <v>127500</v>
-      </c>
-      <c r="R280" s="6" t="n">
-        <v>2932500</v>
-      </c>
-      <c r="S280" s="6" t="n">
-        <v>127500</v>
-      </c>
-      <c r="T280" s="6" t="n">
-        <v>374451500</v>
-      </c>
-      <c r="U280" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s81_90b80c5/zofoGDA_auc_a9a_epochs500_seed81_batch128_gamma0.01_lam0.01_delta0.001q11_log.csv</t>
-        </is>
-      </c>
-      <c r="V280" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s81_90b80c5/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W280" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_a9a_M_11_s81_90b80c5/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X280" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_a9a_M_11_s81_90b80c5.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q280" s="6" t="inlineStr"/>
+      <c r="R280" s="6" t="inlineStr"/>
+      <c r="S280" s="6" t="inlineStr"/>
+      <c r="T280" s="6" t="inlineStr"/>
+      <c r="U280" s="6" t="inlineStr"/>
+      <c r="V280" s="6" t="inlineStr"/>
+      <c r="W280" s="6" t="inlineStr"/>
+      <c r="X280" s="6" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -34816,7 +34126,7 @@
         </is>
       </c>
       <c r="B281" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
@@ -34910,7 +34220,7 @@
         </is>
       </c>
       <c r="B282" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C282" s="6" t="inlineStr">
         <is>
@@ -35004,7 +34314,7 @@
         </is>
       </c>
       <c r="B283" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
@@ -35098,7 +34408,7 @@
         </is>
       </c>
       <c r="B284" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
@@ -35192,7 +34502,7 @@
         </is>
       </c>
       <c r="B285" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
@@ -35380,7 +34690,7 @@
         </is>
       </c>
       <c r="B287" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
@@ -35474,7 +34784,7 @@
         </is>
       </c>
       <c r="B288" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
@@ -35568,7 +34878,7 @@
         </is>
       </c>
       <c r="B289" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
@@ -35662,7 +34972,7 @@
         </is>
       </c>
       <c r="B290" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C290" s="6" t="inlineStr">
         <is>
@@ -35756,7 +35066,7 @@
         </is>
       </c>
       <c r="B291" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
@@ -35850,7 +35160,7 @@
         </is>
       </c>
       <c r="B292" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C292" s="6" t="inlineStr">
         <is>
@@ -36038,7 +35348,7 @@
         </is>
       </c>
       <c r="B294" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
@@ -36132,7 +35442,7 @@
         </is>
       </c>
       <c r="B295" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
@@ -36226,7 +35536,7 @@
         </is>
       </c>
       <c r="B296" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C296" s="6" t="inlineStr">
         <is>
@@ -36320,7 +35630,7 @@
         </is>
       </c>
       <c r="B297" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
@@ -36414,7 +35724,7 @@
         </is>
       </c>
       <c r="B298" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C298" s="6" t="inlineStr">
         <is>
@@ -36508,7 +35818,7 @@
         </is>
       </c>
       <c r="B299" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C299" s="6" t="inlineStr">
         <is>
@@ -36602,7 +35912,7 @@
         </is>
       </c>
       <c r="B300" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C300" s="6" t="inlineStr">
         <is>
@@ -36696,7 +36006,7 @@
         </is>
       </c>
       <c r="B301" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C301" s="6" t="inlineStr">
         <is>
@@ -36790,7 +36100,7 @@
         </is>
       </c>
       <c r="B302" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C302" s="6" t="inlineStr">
         <is>
@@ -36884,7 +36194,7 @@
         </is>
       </c>
       <c r="B303" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C303" s="6" t="inlineStr">
         <is>
@@ -36978,7 +36288,7 @@
         </is>
       </c>
       <c r="B304" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C304" s="6" t="inlineStr">
         <is>
@@ -37072,7 +36382,7 @@
         </is>
       </c>
       <c r="B305" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
@@ -37166,7 +36476,7 @@
         </is>
       </c>
       <c r="B306" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C306" s="6" t="inlineStr">
         <is>
@@ -37260,7 +36570,7 @@
         </is>
       </c>
       <c r="B307" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C307" s="6" t="inlineStr">
         <is>
@@ -37354,7 +36664,7 @@
         </is>
       </c>
       <c r="B308" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C308" s="6" t="inlineStr">
         <is>
@@ -37448,7 +36758,7 @@
         </is>
       </c>
       <c r="B309" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C309" s="6" t="inlineStr">
         <is>
@@ -37542,7 +36852,7 @@
         </is>
       </c>
       <c r="B310" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C310" s="6" t="inlineStr">
         <is>
@@ -37636,7 +36946,7 @@
         </is>
       </c>
       <c r="B311" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C311" s="6" t="inlineStr">
         <is>
@@ -37824,7 +37134,7 @@
         </is>
       </c>
       <c r="B313" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C313" s="6" t="inlineStr">
         <is>
@@ -37918,7 +37228,7 @@
         </is>
       </c>
       <c r="B314" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C314" s="6" t="inlineStr">
         <is>
@@ -38106,7 +37416,7 @@
         </is>
       </c>
       <c r="B316" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C316" s="6" t="inlineStr">
         <is>
@@ -38200,7 +37510,7 @@
         </is>
       </c>
       <c r="B317" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C317" s="6" t="inlineStr">
         <is>
@@ -38294,7 +37604,7 @@
         </is>
       </c>
       <c r="B318" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C318" s="6" t="inlineStr">
         <is>
@@ -38388,7 +37698,7 @@
         </is>
       </c>
       <c r="B319" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C319" s="6" t="inlineStr">
         <is>
@@ -38482,7 +37792,7 @@
         </is>
       </c>
       <c r="B320" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C320" s="6" t="inlineStr">
         <is>
@@ -38576,7 +37886,7 @@
         </is>
       </c>
       <c r="B321" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C321" s="6" t="inlineStr">
         <is>
@@ -38670,7 +37980,7 @@
         </is>
       </c>
       <c r="B322" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C322" s="6" t="inlineStr">
         <is>
@@ -38764,7 +38074,7 @@
         </is>
       </c>
       <c r="B323" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C323" s="6" t="inlineStr">
         <is>
@@ -38858,7 +38168,7 @@
         </is>
       </c>
       <c r="B324" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C324" s="6" t="inlineStr">
         <is>
@@ -38952,7 +38262,7 @@
         </is>
       </c>
       <c r="B325" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C325" s="6" t="inlineStr">
         <is>
@@ -39046,7 +38356,7 @@
         </is>
       </c>
       <c r="B326" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C326" s="6" t="inlineStr">
         <is>
@@ -39140,7 +38450,7 @@
         </is>
       </c>
       <c r="B327" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C327" s="6" t="inlineStr">
         <is>
@@ -39234,7 +38544,7 @@
         </is>
       </c>
       <c r="B328" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C328" s="6" t="inlineStr">
         <is>
@@ -39328,7 +38638,7 @@
         </is>
       </c>
       <c r="B329" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C329" s="6" t="inlineStr">
         <is>
@@ -39516,7 +38826,7 @@
         </is>
       </c>
       <c r="B331" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C331" s="6" t="inlineStr">
         <is>
@@ -39704,7 +39014,7 @@
         </is>
       </c>
       <c r="B333" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C333" s="6" t="inlineStr">
         <is>
@@ -39798,7 +39108,7 @@
         </is>
       </c>
       <c r="B334" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C334" s="6" t="inlineStr">
         <is>
@@ -39892,7 +39202,7 @@
         </is>
       </c>
       <c r="B335" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C335" s="6" t="inlineStr">
         <is>
@@ -39986,7 +39296,7 @@
         </is>
       </c>
       <c r="B336" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C336" s="6" t="inlineStr">
         <is>
@@ -40174,7 +39484,7 @@
         </is>
       </c>
       <c r="B338" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C338" s="6" t="inlineStr">
         <is>
@@ -40268,7 +39578,7 @@
         </is>
       </c>
       <c r="B339" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C339" s="6" t="inlineStr">
         <is>
@@ -40362,7 +39672,7 @@
         </is>
       </c>
       <c r="B340" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C340" s="6" t="inlineStr">
         <is>
@@ -40456,7 +39766,7 @@
         </is>
       </c>
       <c r="B341" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C341" s="6" t="inlineStr">
         <is>
@@ -40550,7 +39860,7 @@
         </is>
       </c>
       <c r="B342" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C342" s="6" t="inlineStr">
         <is>
@@ -40644,7 +39954,7 @@
         </is>
       </c>
       <c r="B343" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C343" s="6" t="inlineStr">
         <is>
@@ -40734,7 +40044,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_ijcnn1_M_4_s14_a076189</t>
+          <t>auc_zofosgda_ijcnn1_M_55_s14_eff6e27</t>
         </is>
       </c>
       <c r="B344" s="6" t="n">
@@ -40757,78 +40067,40 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G344" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H344" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I344" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L344" s="6" t="n">
-        <v>0.8845314639667289</v>
-      </c>
-      <c r="M344" s="6" t="n">
-        <v>0.8847000836218498</v>
-      </c>
-      <c r="N344" s="6" t="n">
-        <v>499</v>
-      </c>
-      <c r="O344" s="6" t="n">
-        <v>2275.828</v>
-      </c>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I344" s="6" t="inlineStr"/>
+      <c r="J344" s="6" t="inlineStr"/>
+      <c r="K344" s="6" t="inlineStr"/>
+      <c r="L344" s="6" t="inlineStr"/>
+      <c r="M344" s="6" t="inlineStr"/>
+      <c r="N344" s="6" t="inlineStr"/>
+      <c r="O344" s="6" t="inlineStr"/>
       <c r="P344" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q344" s="6" t="n">
-        <v>195500</v>
-      </c>
-      <c r="R344" s="6" t="n">
-        <v>1759500</v>
-      </c>
-      <c r="S344" s="6" t="n">
-        <v>195500</v>
-      </c>
-      <c r="T344" s="6" t="n">
-        <v>224955000</v>
-      </c>
-      <c r="U344" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s14_a076189/zofoGDA_auc_ijcnn1_epochs500_seed14_batch128_gamma0.01_lam0.01_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V344" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s14_a076189/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W344" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s14_a076189/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X344" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_ijcnn1_M_4_s14_a076189.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q344" s="6" t="inlineStr"/>
+      <c r="R344" s="6" t="inlineStr"/>
+      <c r="S344" s="6" t="inlineStr"/>
+      <c r="T344" s="6" t="inlineStr"/>
+      <c r="U344" s="6" t="inlineStr"/>
+      <c r="V344" s="6" t="inlineStr"/>
+      <c r="W344" s="6" t="inlineStr"/>
+      <c r="X344" s="6" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_ijcnn1_M_4_s42_2929ef8</t>
+          <t>auc_zofosgda_ijcnn1_M_55_s42_729f8a7</t>
         </is>
       </c>
       <c r="B345" s="6" t="n">
@@ -40851,78 +40123,40 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G345" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H345" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I345" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L345" s="6" t="n">
-        <v>0.8869507626633094</v>
-      </c>
-      <c r="M345" s="6" t="n">
-        <v>0.8877742099483316</v>
-      </c>
-      <c r="N345" s="6" t="n">
-        <v>473</v>
-      </c>
-      <c r="O345" s="6" t="n">
-        <v>2269.748</v>
-      </c>
+      <c r="H345" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I345" s="6" t="inlineStr"/>
+      <c r="J345" s="6" t="inlineStr"/>
+      <c r="K345" s="6" t="inlineStr"/>
+      <c r="L345" s="6" t="inlineStr"/>
+      <c r="M345" s="6" t="inlineStr"/>
+      <c r="N345" s="6" t="inlineStr"/>
+      <c r="O345" s="6" t="inlineStr"/>
       <c r="P345" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q345" s="6" t="n">
-        <v>195500</v>
-      </c>
-      <c r="R345" s="6" t="n">
-        <v>1759500</v>
-      </c>
-      <c r="S345" s="6" t="n">
-        <v>195500</v>
-      </c>
-      <c r="T345" s="6" t="n">
-        <v>224955000</v>
-      </c>
-      <c r="U345" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s42_2929ef8/zofoGDA_auc_ijcnn1_epochs500_seed42_batch128_gamma0.01_lam0.01_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V345" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s42_2929ef8/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W345" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s42_2929ef8/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X345" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_ijcnn1_M_4_s42_2929ef8.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q345" s="6" t="inlineStr"/>
+      <c r="R345" s="6" t="inlineStr"/>
+      <c r="S345" s="6" t="inlineStr"/>
+      <c r="T345" s="6" t="inlineStr"/>
+      <c r="U345" s="6" t="inlineStr"/>
+      <c r="V345" s="6" t="inlineStr"/>
+      <c r="W345" s="6" t="inlineStr"/>
+      <c r="X345" s="6" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>auc_zofosgda_ijcnn1_M_4_s81_b836124</t>
+          <t>auc_zofosgda_ijcnn1_M_55_s81_ac604d6</t>
         </is>
       </c>
       <c r="B346" s="6" t="n">
@@ -40945,73 +40179,35 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G346" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="H346" s="8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I346" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L346" s="6" t="n">
-        <v>0.8805007305072365</v>
-      </c>
-      <c r="M346" s="6" t="n">
-        <v>0.8806889007745996</v>
-      </c>
-      <c r="N346" s="6" t="n">
-        <v>498</v>
-      </c>
-      <c r="O346" s="6" t="n">
-        <v>2280.361</v>
-      </c>
+      <c r="H346" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I346" s="6" t="inlineStr"/>
+      <c r="J346" s="6" t="inlineStr"/>
+      <c r="K346" s="6" t="inlineStr"/>
+      <c r="L346" s="6" t="inlineStr"/>
+      <c r="M346" s="6" t="inlineStr"/>
+      <c r="N346" s="6" t="inlineStr"/>
+      <c r="O346" s="6" t="inlineStr"/>
       <c r="P346" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q346" s="6" t="n">
-        <v>195500</v>
-      </c>
-      <c r="R346" s="6" t="n">
-        <v>1759500</v>
-      </c>
-      <c r="S346" s="6" t="n">
-        <v>195500</v>
-      </c>
-      <c r="T346" s="6" t="n">
-        <v>224955000</v>
-      </c>
-      <c r="U346" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s81_b836124/zofoGDA_auc_ijcnn1_epochs500_seed81_batch128_gamma0.01_lam0.01_delta0.001q4_log.csv</t>
-        </is>
-      </c>
-      <c r="V346" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s81_b836124/epoch_times.csv</t>
-        </is>
-      </c>
-      <c r="W346" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/runs/auc_zofosgda_ijcnn1_M_4_s81_b836124/gpu_audit_attempt1.csv</t>
-        </is>
-      </c>
-      <c r="X346" s="6" t="inlineStr">
-        <is>
-          <t>/hy-tmp/ZOFOGDA_Nips26/rebuttal_auc_original/logs/auc_zofosgda_ijcnn1_M_4_s81_b836124.log</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q346" s="6" t="inlineStr"/>
+      <c r="R346" s="6" t="inlineStr"/>
+      <c r="S346" s="6" t="inlineStr"/>
+      <c r="T346" s="6" t="inlineStr"/>
+      <c r="U346" s="6" t="inlineStr"/>
+      <c r="V346" s="6" t="inlineStr"/>
+      <c r="W346" s="6" t="inlineStr"/>
+      <c r="X346" s="6" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
@@ -41208,7 +40404,7 @@
         </is>
       </c>
       <c r="B349" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C349" s="6" t="inlineStr">
         <is>
@@ -41302,7 +40498,7 @@
         </is>
       </c>
       <c r="B350" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C350" s="6" t="inlineStr">
         <is>
@@ -41490,7 +40686,7 @@
         </is>
       </c>
       <c r="B352" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C352" s="6" t="inlineStr">
         <is>
@@ -41584,7 +40780,7 @@
         </is>
       </c>
       <c r="B353" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C353" s="6" t="inlineStr">
         <is>
@@ -41678,7 +40874,7 @@
         </is>
       </c>
       <c r="B354" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C354" s="6" t="inlineStr">
         <is>
@@ -41866,7 +41062,7 @@
         </is>
       </c>
       <c r="B356" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C356" s="6" t="inlineStr">
         <is>
@@ -41960,7 +41156,7 @@
         </is>
       </c>
       <c r="B357" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C357" s="6" t="inlineStr">
         <is>
@@ -42054,7 +41250,7 @@
         </is>
       </c>
       <c r="B358" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C358" s="6" t="inlineStr">
         <is>
@@ -42148,7 +41344,7 @@
         </is>
       </c>
       <c r="B359" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C359" s="6" t="inlineStr">
         <is>
@@ -42336,7 +41532,7 @@
         </is>
       </c>
       <c r="B361" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C361" s="6" t="inlineStr">
         <is>
@@ -42430,7 +41626,7 @@
         </is>
       </c>
       <c r="B362" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C362" s="6" t="inlineStr">
         <is>
@@ -42524,7 +41720,7 @@
         </is>
       </c>
       <c r="B363" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C363" s="6" t="inlineStr">
         <is>
@@ -42618,7 +41814,7 @@
         </is>
       </c>
       <c r="B364" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C364" s="6" t="inlineStr">
         <is>
@@ -42712,7 +41908,7 @@
         </is>
       </c>
       <c r="B365" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C365" s="6" t="inlineStr">
         <is>
@@ -42994,7 +42190,7 @@
         </is>
       </c>
       <c r="B368" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C368" s="6" t="inlineStr">
         <is>
@@ -43088,7 +42284,7 @@
         </is>
       </c>
       <c r="B369" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C369" s="6" t="inlineStr">
         <is>
@@ -43182,7 +42378,7 @@
         </is>
       </c>
       <c r="B370" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
@@ -43276,7 +42472,7 @@
         </is>
       </c>
       <c r="B371" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C371" s="6" t="inlineStr">
         <is>
@@ -43370,7 +42566,7 @@
         </is>
       </c>
       <c r="B372" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C372" s="6" t="inlineStr">
         <is>
@@ -43558,7 +42754,7 @@
         </is>
       </c>
       <c r="B374" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C374" s="6" t="inlineStr">
         <is>
@@ -43652,7 +42848,7 @@
         </is>
       </c>
       <c r="B375" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C375" s="6" t="inlineStr">
         <is>
@@ -43746,7 +42942,7 @@
         </is>
       </c>
       <c r="B376" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C376" s="6" t="inlineStr">
         <is>
@@ -43840,7 +43036,7 @@
         </is>
       </c>
       <c r="B377" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C377" s="6" t="inlineStr">
         <is>
@@ -43934,7 +43130,7 @@
         </is>
       </c>
       <c r="B378" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C378" s="6" t="inlineStr">
         <is>
@@ -44028,7 +43224,7 @@
         </is>
       </c>
       <c r="B379" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C379" s="6" t="inlineStr">
         <is>
@@ -44166,7 +43362,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T18:08:31+08:00</t>
+          <t>2026-07-28T11:30:11+08:00</t>
         </is>
       </c>
     </row>
@@ -44187,7 +43383,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
@@ -44217,7 +43413,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -44228,7 +43424,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>95.2%</t>
         </is>
       </c>
     </row>
